--- a/data_voor_swing/aggregatietabellen/kern_gewest.xlsx
+++ b/data_voor_swing/aggregatietabellen/kern_gewest.xlsx
@@ -1,57 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <workbookPr showObjects="all" updateLinks="userSet" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" xWindow="480" yWindow="75" windowWidth="18075" windowHeight="12525" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="kern_gewest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="auto" refMode="A1" iterateCount="100"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.000000000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
-    <numFmt numFmtId="175" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="0.000000000000"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="179" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="180" formatCode="0.0000000000000000"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,41 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -381,2973 +420,3567 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B296"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="0" outlineLevel="0">
-      <c r="A1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>kern</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gewest</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:2" s="0" outlineLevel="0">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>71002_1</t>
         </is>
       </c>
-      <c r="B2" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="0" outlineLevel="0">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>71002_2</t>
         </is>
       </c>
-      <c r="B3" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="0" outlineLevel="0">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>71002_3</t>
         </is>
       </c>
-      <c r="B4" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="0" outlineLevel="0">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>71002_4</t>
         </is>
       </c>
-      <c r="B5" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="0" outlineLevel="0">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>71004_1</t>
         </is>
       </c>
-      <c r="B6" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="0" outlineLevel="0">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>71004_2</t>
         </is>
       </c>
-      <c r="B7" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="0" outlineLevel="0">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>71004_3</t>
         </is>
       </c>
-      <c r="B8" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="0" outlineLevel="0">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>71004_4</t>
         </is>
       </c>
-      <c r="B9" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="0" outlineLevel="0">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>71004_5</t>
         </is>
       </c>
-      <c r="B10" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="0" outlineLevel="0">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>71004_6</t>
         </is>
       </c>
-      <c r="B11" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="0" outlineLevel="0">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>71004_7</t>
         </is>
       </c>
-      <c r="B12" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="0" outlineLevel="0">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>71004_8</t>
         </is>
       </c>
-      <c r="B13" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="0" outlineLevel="0">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>71011_1</t>
         </is>
       </c>
-      <c r="B14" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="0" outlineLevel="0">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>71011_2</t>
         </is>
       </c>
-      <c r="B15" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" s="0" outlineLevel="0">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>71011_3</t>
         </is>
       </c>
-      <c r="B16" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="0" outlineLevel="0">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>71011_4</t>
         </is>
       </c>
-      <c r="B17" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" s="0" outlineLevel="0">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>71011_5</t>
         </is>
       </c>
-      <c r="B18" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="0" outlineLevel="0">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>71011_6</t>
         </is>
       </c>
-      <c r="B19" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" s="0" outlineLevel="0">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>71016_1</t>
         </is>
       </c>
-      <c r="B20" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" s="0" outlineLevel="0">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>71016_10</t>
         </is>
       </c>
-      <c r="B21" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" s="0" outlineLevel="0">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>71016_11</t>
         </is>
       </c>
-      <c r="B22" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" s="0" outlineLevel="0">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>71016_12</t>
         </is>
       </c>
-      <c r="B23" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" s="0" outlineLevel="0">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>71016_13</t>
         </is>
       </c>
-      <c r="B24" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" s="0" outlineLevel="0">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>71016_14</t>
         </is>
       </c>
-      <c r="B25" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" s="0" outlineLevel="0">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>71016_2</t>
         </is>
       </c>
-      <c r="B26" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" s="0" outlineLevel="0">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>71016_3</t>
         </is>
       </c>
-      <c r="B27" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" s="0" outlineLevel="0">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>71016_4</t>
         </is>
       </c>
-      <c r="B28" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" s="0" outlineLevel="0">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>71016_5</t>
         </is>
       </c>
-      <c r="B29" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="0" outlineLevel="0">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>71016_6</t>
         </is>
       </c>
-      <c r="B30" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" s="0" outlineLevel="0">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>71016_7</t>
         </is>
       </c>
-      <c r="B31" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" s="0" outlineLevel="0">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>71016_8</t>
         </is>
       </c>
-      <c r="B32" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" s="0" outlineLevel="0">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>71016_9</t>
         </is>
       </c>
-      <c r="B33" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" s="0" outlineLevel="0">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>71017_1</t>
         </is>
       </c>
-      <c r="B34" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" s="0" outlineLevel="0">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>71017_2</t>
         </is>
       </c>
-      <c r="B35" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" s="0" outlineLevel="0">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>71017_3</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" s="0" outlineLevel="0">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>71017_4</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" s="0" outlineLevel="0">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>71017_5</t>
         </is>
       </c>
-      <c r="B38" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" s="0" outlineLevel="0">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>71017_6</t>
         </is>
       </c>
-      <c r="B39" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" s="0" outlineLevel="0">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>71017_7</t>
         </is>
       </c>
-      <c r="B40" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" s="0" outlineLevel="0">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="inlineStr">
         <is>
           <t>71020_1</t>
         </is>
       </c>
-      <c r="B41" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" s="0" outlineLevel="0">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>71020_2</t>
         </is>
       </c>
-      <c r="B42" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" s="0" outlineLevel="0">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>71020_3</t>
         </is>
       </c>
-      <c r="B43" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" s="0" outlineLevel="0">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>71022_1</t>
         </is>
       </c>
-      <c r="B44" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" s="0" outlineLevel="0">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="inlineStr">
         <is>
           <t>71022_10</t>
         </is>
       </c>
-      <c r="B45" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" s="0" outlineLevel="0">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="inlineStr">
         <is>
           <t>71022_11</t>
         </is>
       </c>
-      <c r="B46" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" s="0" outlineLevel="0">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="inlineStr">
         <is>
           <t>71022_12</t>
         </is>
       </c>
-      <c r="B47" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" s="0" outlineLevel="0">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>71022_13</t>
         </is>
       </c>
-      <c r="B48" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" s="0" outlineLevel="0">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
           <t>71022_2</t>
         </is>
       </c>
-      <c r="B49" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" s="0" outlineLevel="0">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>71022_3</t>
         </is>
       </c>
-      <c r="B50" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" s="0" outlineLevel="0">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>71022_4</t>
         </is>
       </c>
-      <c r="B51" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" s="0" outlineLevel="0">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>71022_5</t>
         </is>
       </c>
-      <c r="B52" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" s="0" outlineLevel="0">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>71022_6</t>
         </is>
       </c>
-      <c r="B53" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" s="0" outlineLevel="0">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>71022_7</t>
         </is>
       </c>
-      <c r="B54" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" s="0" outlineLevel="0">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
           <t>71022_8</t>
         </is>
       </c>
-      <c r="B55" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" s="0" outlineLevel="0">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" t="inlineStr">
         <is>
           <t>71022_9</t>
         </is>
       </c>
-      <c r="B56" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" s="0" outlineLevel="0">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>71024_1</t>
         </is>
       </c>
-      <c r="B57" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" s="0" outlineLevel="0">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" t="inlineStr">
         <is>
           <t>71024_2</t>
         </is>
       </c>
-      <c r="B58" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" s="0" outlineLevel="0">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>71024_3</t>
         </is>
       </c>
-      <c r="B59" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" s="0" outlineLevel="0">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" t="inlineStr">
         <is>
           <t>71024_4</t>
         </is>
       </c>
-      <c r="B60" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" s="0" outlineLevel="0">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>71024_5</t>
         </is>
       </c>
-      <c r="B61" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" s="0" outlineLevel="0">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>71034_2</t>
         </is>
       </c>
-      <c r="B62" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" s="0" outlineLevel="0">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>71034_3</t>
         </is>
       </c>
-      <c r="B63" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" s="0" outlineLevel="0">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" t="inlineStr">
         <is>
           <t>71034_4</t>
         </is>
       </c>
-      <c r="B64" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" s="0" outlineLevel="0">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>71037_1</t>
         </is>
       </c>
-      <c r="B65" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" s="0" outlineLevel="0">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>71037_2</t>
         </is>
       </c>
-      <c r="B66" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" s="0" outlineLevel="0">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>71037_3</t>
         </is>
       </c>
-      <c r="B67" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" s="0" outlineLevel="0">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" t="inlineStr">
         <is>
           <t>71037_4</t>
         </is>
       </c>
-      <c r="B68" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" s="0" outlineLevel="0">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>71037_5</t>
         </is>
       </c>
-      <c r="B69" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" s="0" outlineLevel="0">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
           <t>71037_6</t>
         </is>
       </c>
-      <c r="B70" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" s="0" outlineLevel="0">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
           <t>71045_1</t>
         </is>
       </c>
-      <c r="B71" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" s="0" outlineLevel="0">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
           <t>71045_2</t>
         </is>
       </c>
-      <c r="B72" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" s="0" outlineLevel="0">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>71045_3</t>
         </is>
       </c>
-      <c r="B73" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" s="0" outlineLevel="0">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" t="inlineStr">
         <is>
           <t>71045_4</t>
         </is>
       </c>
-      <c r="B74" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" s="0" outlineLevel="0">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" t="inlineStr">
         <is>
           <t>71053_1</t>
         </is>
       </c>
-      <c r="B75" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" s="0" outlineLevel="0">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
           <t>71053_10</t>
         </is>
       </c>
-      <c r="B76" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" s="0" outlineLevel="0">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
           <t>71053_11</t>
         </is>
       </c>
-      <c r="B77" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" s="0" outlineLevel="0">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
           <t>71053_12</t>
         </is>
       </c>
-      <c r="B78" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" s="0" outlineLevel="0">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
           <t>71053_13</t>
         </is>
       </c>
-      <c r="B79" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" s="0" outlineLevel="0">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>71053_14</t>
         </is>
       </c>
-      <c r="B80" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" s="0" outlineLevel="0">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
           <t>71053_15</t>
         </is>
       </c>
-      <c r="B81" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" s="0" outlineLevel="0">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" t="inlineStr">
         <is>
           <t>71053_16</t>
         </is>
       </c>
-      <c r="B82" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" s="0" outlineLevel="0">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" t="inlineStr">
         <is>
           <t>71053_17</t>
         </is>
       </c>
-      <c r="B83" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" s="0" outlineLevel="0">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" t="inlineStr">
         <is>
           <t>71053_18</t>
         </is>
       </c>
-      <c r="B84" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" s="0" outlineLevel="0">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" t="inlineStr">
         <is>
           <t>71053_2</t>
         </is>
       </c>
-      <c r="B85" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" s="0" outlineLevel="0">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" t="inlineStr">
         <is>
           <t>71053_3</t>
         </is>
       </c>
-      <c r="B86" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" s="0" outlineLevel="0">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
       <c r="A87" t="inlineStr">
         <is>
           <t>71053_4</t>
         </is>
       </c>
-      <c r="B87" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" s="0" outlineLevel="0">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
       <c r="A88" t="inlineStr">
         <is>
           <t>71053_5</t>
         </is>
       </c>
-      <c r="B88" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" s="0" outlineLevel="0">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
           <t>71053_6</t>
         </is>
       </c>
-      <c r="B89" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" s="0" outlineLevel="0">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90" t="inlineStr">
         <is>
           <t>71053_7</t>
         </is>
       </c>
-      <c r="B90" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" s="0" outlineLevel="0">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
       <c r="A91" t="inlineStr">
         <is>
           <t>71053_8</t>
         </is>
       </c>
-      <c r="B91" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" s="0" outlineLevel="0">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92" t="inlineStr">
         <is>
           <t>71053_9</t>
         </is>
       </c>
-      <c r="B92" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" s="0" outlineLevel="0">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" t="inlineStr">
         <is>
           <t>71057_1</t>
         </is>
       </c>
-      <c r="B93" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" s="0" outlineLevel="0">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94" t="inlineStr">
         <is>
           <t>71057_2</t>
         </is>
       </c>
-      <c r="B94" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" s="0" outlineLevel="0">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" t="inlineStr">
         <is>
           <t>71057_3</t>
         </is>
       </c>
-      <c r="B95" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" s="0" outlineLevel="0">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
       <c r="A96" t="inlineStr">
         <is>
           <t>71057_4</t>
         </is>
       </c>
-      <c r="B96" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" s="0" outlineLevel="0">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" t="inlineStr">
         <is>
           <t>71066_1</t>
         </is>
       </c>
-      <c r="B97" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" s="0" outlineLevel="0">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
       <c r="A98" t="inlineStr">
         <is>
           <t>71066_2</t>
         </is>
       </c>
-      <c r="B98" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" s="0" outlineLevel="0">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" t="inlineStr">
         <is>
           <t>71066_3</t>
         </is>
       </c>
-      <c r="B99" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" s="0" outlineLevel="0">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" t="inlineStr">
         <is>
           <t>71066_4</t>
         </is>
       </c>
-      <c r="B100" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" s="0" outlineLevel="0">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
       <c r="A101" t="inlineStr">
         <is>
           <t>71067_1</t>
         </is>
       </c>
-      <c r="B101" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" s="0" outlineLevel="0">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
       <c r="A102" t="inlineStr">
         <is>
           <t>71067_2</t>
         </is>
       </c>
-      <c r="B102" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" s="0" outlineLevel="0">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" t="inlineStr">
         <is>
           <t>71067_3</t>
         </is>
       </c>
-      <c r="B103" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" s="0" outlineLevel="0">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" t="inlineStr">
         <is>
           <t>71067_4</t>
         </is>
       </c>
-      <c r="B104" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" s="0" outlineLevel="0">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" t="inlineStr">
         <is>
           <t>71069_1</t>
         </is>
       </c>
-      <c r="B105" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" s="0" outlineLevel="0">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
       <c r="A106" t="inlineStr">
         <is>
           <t>71069_2</t>
         </is>
       </c>
-      <c r="B106" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" s="0" outlineLevel="0">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
       <c r="A107" t="inlineStr">
         <is>
           <t>71069_3</t>
         </is>
       </c>
-      <c r="B107" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" s="0" outlineLevel="0">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
       <c r="A108" t="inlineStr">
         <is>
           <t>71070_1</t>
         </is>
       </c>
-      <c r="B108" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" s="0" outlineLevel="0">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
       <c r="A109" t="inlineStr">
         <is>
           <t>71070_2</t>
         </is>
       </c>
-      <c r="B109" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" s="0" outlineLevel="0">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
       <c r="A110" t="inlineStr">
         <is>
           <t>71070_3</t>
         </is>
       </c>
-      <c r="B110" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" s="0" outlineLevel="0">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
       <c r="A111" t="inlineStr">
         <is>
           <t>71070_4</t>
         </is>
       </c>
-      <c r="B111" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" s="0" outlineLevel="0">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
       <c r="A112" t="inlineStr">
         <is>
           <t>71070_5</t>
         </is>
       </c>
-      <c r="B112" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" s="0" outlineLevel="0">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" t="inlineStr">
         <is>
           <t>71070_6</t>
         </is>
       </c>
-      <c r="B113" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" s="0" outlineLevel="0">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
       <c r="A114" t="inlineStr">
         <is>
           <t>71070_7</t>
         </is>
       </c>
-      <c r="B114" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" s="0" outlineLevel="0">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
       <c r="A115" t="inlineStr">
         <is>
           <t>71070_8</t>
         </is>
       </c>
-      <c r="B115" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" s="0" outlineLevel="0">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
       <c r="A116" t="inlineStr">
         <is>
           <t>71070_9</t>
         </is>
       </c>
-      <c r="B116" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" s="0" outlineLevel="0">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
       <c r="A117" t="inlineStr">
         <is>
           <t>72003_1</t>
         </is>
       </c>
-      <c r="B117" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" s="0" outlineLevel="0">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
       <c r="A118" t="inlineStr">
         <is>
           <t>72003_2</t>
         </is>
       </c>
-      <c r="B118" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" s="0" outlineLevel="0">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
       <c r="A119" t="inlineStr">
         <is>
           <t>72003_3</t>
         </is>
       </c>
-      <c r="B119" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" s="0" outlineLevel="0">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
       <c r="A120" t="inlineStr">
         <is>
           <t>72003_4</t>
         </is>
       </c>
-      <c r="B120" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" s="0" outlineLevel="0">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>72003_5</t>
         </is>
       </c>
-      <c r="B121" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" s="0" outlineLevel="0">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
       <c r="A122" t="inlineStr">
         <is>
           <t>72004_1</t>
         </is>
       </c>
-      <c r="B122" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" s="0" outlineLevel="0">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
       <c r="A123" t="inlineStr">
         <is>
           <t>72004_2</t>
         </is>
       </c>
-      <c r="B123" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" s="0" outlineLevel="0">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
       <c r="A124" t="inlineStr">
         <is>
           <t>72004_3</t>
         </is>
       </c>
-      <c r="B124" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" s="0" outlineLevel="0">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
       <c r="A125" t="inlineStr">
         <is>
           <t>72004_4</t>
         </is>
       </c>
-      <c r="B125" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" s="0" outlineLevel="0">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
       <c r="A126" t="inlineStr">
         <is>
           <t>72004_5</t>
         </is>
       </c>
-      <c r="B126" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" s="0" outlineLevel="0">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
       <c r="A127" t="inlineStr">
         <is>
           <t>72018_1</t>
         </is>
       </c>
-      <c r="B127" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" s="0" outlineLevel="0">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
       <c r="A128" t="inlineStr">
         <is>
           <t>72018_2</t>
         </is>
       </c>
-      <c r="B128" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" s="0" outlineLevel="0">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
       <c r="A129" t="inlineStr">
         <is>
           <t>72018_3</t>
         </is>
       </c>
-      <c r="B129" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" s="0" outlineLevel="0">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
       <c r="A130" t="inlineStr">
         <is>
           <t>72018_4</t>
         </is>
       </c>
-      <c r="B130" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" s="0" outlineLevel="0">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
       <c r="A131" t="inlineStr">
         <is>
           <t>72018_5</t>
         </is>
       </c>
-      <c r="B131" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" s="0" outlineLevel="0">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
       <c r="A132" t="inlineStr">
         <is>
           <t>72020_1</t>
         </is>
       </c>
-      <c r="B132" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" s="0" outlineLevel="0">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
       <c r="A133" t="inlineStr">
         <is>
           <t>72020_10</t>
         </is>
       </c>
-      <c r="B133" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" s="0" outlineLevel="0">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
       <c r="A134" t="inlineStr">
         <is>
           <t>72020_2</t>
         </is>
       </c>
-      <c r="B134" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" s="0" outlineLevel="0">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
       <c r="A135" t="inlineStr">
         <is>
           <t>72020_3</t>
         </is>
       </c>
-      <c r="B135" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" s="0" outlineLevel="0">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>72020_4</t>
         </is>
       </c>
-      <c r="B136" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" s="0" outlineLevel="0">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
       <c r="A137" t="inlineStr">
         <is>
           <t>72020_5</t>
         </is>
       </c>
-      <c r="B137" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" s="0" outlineLevel="0">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
       <c r="A138" t="inlineStr">
         <is>
           <t>72020_6</t>
         </is>
       </c>
-      <c r="B138" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" s="0" outlineLevel="0">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
       <c r="A139" t="inlineStr">
         <is>
           <t>72020_7</t>
         </is>
       </c>
-      <c r="B139" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" s="0" outlineLevel="0">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
       <c r="A140" t="inlineStr">
         <is>
           <t>72020_8</t>
         </is>
       </c>
-      <c r="B140" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" s="0" outlineLevel="0">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
       <c r="A141" t="inlineStr">
         <is>
           <t>72020_9</t>
         </is>
       </c>
-      <c r="B141" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" s="0" outlineLevel="0">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
       <c r="A142" t="inlineStr">
         <is>
           <t>72021_1</t>
         </is>
       </c>
-      <c r="B142" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" s="0" outlineLevel="0">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
       <c r="A143" t="inlineStr">
         <is>
           <t>72021_2</t>
         </is>
       </c>
-      <c r="B143" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" s="0" outlineLevel="0">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
       <c r="A144" t="inlineStr">
         <is>
           <t>72021_3</t>
         </is>
       </c>
-      <c r="B144" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" s="0" outlineLevel="0">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
       <c r="A145" t="inlineStr">
         <is>
           <t>72021_4</t>
         </is>
       </c>
-      <c r="B145" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" s="0" outlineLevel="0">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
       <c r="A146" t="inlineStr">
         <is>
           <t>72021_5</t>
         </is>
       </c>
-      <c r="B146" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" s="0" outlineLevel="0">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
       <c r="A147" t="inlineStr">
         <is>
           <t>72021_6</t>
         </is>
       </c>
-      <c r="B147" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" s="0" outlineLevel="0">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
       <c r="A148" t="inlineStr">
         <is>
           <t>72021_7</t>
         </is>
       </c>
-      <c r="B148" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" s="0" outlineLevel="0">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
       <c r="A149" t="inlineStr">
         <is>
           <t>72030_1</t>
         </is>
       </c>
-      <c r="B149" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" s="0" outlineLevel="0">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>72030_2</t>
         </is>
       </c>
-      <c r="B150" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" s="0" outlineLevel="0">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
       <c r="A151" t="inlineStr">
         <is>
           <t>72030_3</t>
         </is>
       </c>
-      <c r="B151" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" s="0" outlineLevel="0">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
       <c r="A152" t="inlineStr">
         <is>
           <t>72030_4</t>
         </is>
       </c>
-      <c r="B152" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" s="0" outlineLevel="0">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
       <c r="A153" t="inlineStr">
         <is>
           <t>72030_5</t>
         </is>
       </c>
-      <c r="B153" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" s="0" outlineLevel="0">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
       <c r="A154" t="inlineStr">
         <is>
           <t>72030_6</t>
         </is>
       </c>
-      <c r="B154" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" s="0" outlineLevel="0">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
       <c r="A155" t="inlineStr">
         <is>
           <t>72037_1</t>
         </is>
       </c>
-      <c r="B155" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" s="0" outlineLevel="0">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
       <c r="A156" t="inlineStr">
         <is>
           <t>72037_2</t>
         </is>
       </c>
-      <c r="B156" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" s="0" outlineLevel="0">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
       <c r="A157" t="inlineStr">
         <is>
           <t>72037_3</t>
         </is>
       </c>
-      <c r="B157" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" s="0" outlineLevel="0">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
       <c r="A158" t="inlineStr">
         <is>
           <t>72037_4</t>
         </is>
       </c>
-      <c r="B158" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" s="0" outlineLevel="0">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
       <c r="A159" t="inlineStr">
         <is>
           <t>72038_1</t>
         </is>
       </c>
-      <c r="B159" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" s="0" outlineLevel="0">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
       <c r="A160" t="inlineStr">
         <is>
           <t>72038_2</t>
         </is>
       </c>
-      <c r="B160" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" s="0" outlineLevel="0">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
       <c r="A161" t="inlineStr">
         <is>
           <t>72038_3</t>
         </is>
       </c>
-      <c r="B161" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" s="0" outlineLevel="0">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
       <c r="A162" t="inlineStr">
         <is>
           <t>72039_1</t>
         </is>
       </c>
-      <c r="B162" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" s="0" outlineLevel="0">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
       <c r="A163" t="inlineStr">
         <is>
           <t>72039_2</t>
         </is>
       </c>
-      <c r="B163" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" s="0" outlineLevel="0">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
       <c r="A164" t="inlineStr">
         <is>
           <t>72039_3</t>
         </is>
       </c>
-      <c r="B164" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" s="0" outlineLevel="0">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
       <c r="A165" t="inlineStr">
         <is>
           <t>72039_5</t>
         </is>
       </c>
-      <c r="B165" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" s="0" outlineLevel="0">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
       <c r="A166" t="inlineStr">
         <is>
           <t>72039_6</t>
         </is>
       </c>
-      <c r="B166" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" s="0" outlineLevel="0">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
       <c r="A167" t="inlineStr">
         <is>
           <t>72039_7</t>
         </is>
       </c>
-      <c r="B167" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" s="0" outlineLevel="0">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
       <c r="A168" t="inlineStr">
         <is>
           <t>72041_1</t>
         </is>
       </c>
-      <c r="B168" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" s="0" outlineLevel="0">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
       <c r="A169" t="inlineStr">
         <is>
           <t>72041_2</t>
         </is>
       </c>
-      <c r="B169" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" s="0" outlineLevel="0">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
       <c r="A170" t="inlineStr">
         <is>
           <t>72041_3</t>
         </is>
       </c>
-      <c r="B170" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" s="0" outlineLevel="0">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
       <c r="A171" t="inlineStr">
         <is>
           <t>72041_5</t>
         </is>
       </c>
-      <c r="B171" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" s="0" outlineLevel="0">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
       <c r="A172" t="inlineStr">
         <is>
           <t>72041_6</t>
         </is>
       </c>
-      <c r="B172" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" s="0" outlineLevel="0">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
       <c r="A173" t="inlineStr">
         <is>
           <t>72042_1</t>
         </is>
       </c>
-      <c r="B173" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" s="0" outlineLevel="0">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
       <c r="A174" t="inlineStr">
         <is>
           <t>72042_2</t>
         </is>
       </c>
-      <c r="B174" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" s="0" outlineLevel="0">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
       <c r="A175" t="inlineStr">
         <is>
           <t>72042_3</t>
         </is>
       </c>
-      <c r="B175" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" s="0" outlineLevel="0">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
       <c r="A176" t="inlineStr">
         <is>
           <t>72042_4</t>
         </is>
       </c>
-      <c r="B176" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" s="0" outlineLevel="0">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
       <c r="A177" t="inlineStr">
         <is>
           <t>72042_5</t>
         </is>
       </c>
-      <c r="B177" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" s="0" outlineLevel="0">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
       <c r="A178" t="inlineStr">
         <is>
           <t>72042_6</t>
         </is>
       </c>
-      <c r="B178" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" s="0" outlineLevel="0">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
       <c r="A179" t="inlineStr">
         <is>
           <t>72042_7</t>
         </is>
       </c>
-      <c r="B179" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" s="0" outlineLevel="0">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
       <c r="A180" t="inlineStr">
         <is>
           <t>72042_8</t>
         </is>
       </c>
-      <c r="B180" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" s="0" outlineLevel="0">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
       <c r="A181" t="inlineStr">
         <is>
           <t>72043_1</t>
         </is>
       </c>
-      <c r="B181" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" s="0" outlineLevel="0">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
       <c r="A182" t="inlineStr">
         <is>
           <t>72043_2</t>
         </is>
       </c>
-      <c r="B182" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" s="0" outlineLevel="0">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
       <c r="A183" t="inlineStr">
         <is>
           <t>72043_3</t>
         </is>
       </c>
-      <c r="B183" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" s="0" outlineLevel="0">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
       <c r="A184" t="inlineStr">
         <is>
           <t>72043_4</t>
         </is>
       </c>
-      <c r="B184" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" s="0" outlineLevel="0">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
       <c r="A185" t="inlineStr">
         <is>
           <t>72043_5</t>
         </is>
       </c>
-      <c r="B185" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" s="0" outlineLevel="0">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
       <c r="A186" t="inlineStr">
         <is>
           <t>72043_6</t>
         </is>
       </c>
-      <c r="B186" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" s="0" outlineLevel="0">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
       <c r="A187" t="inlineStr">
         <is>
           <t>72043_7</t>
         </is>
       </c>
-      <c r="B187" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" s="0" outlineLevel="0">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
       <c r="A188" t="inlineStr">
         <is>
           <t>72043_8</t>
         </is>
       </c>
-      <c r="B188" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" s="0" outlineLevel="0">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
       <c r="A189" t="inlineStr">
         <is>
           <t>72043_9</t>
         </is>
       </c>
-      <c r="B189" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" s="0" outlineLevel="0">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
       <c r="A190" t="inlineStr">
         <is>
           <t>73001_1</t>
         </is>
       </c>
-      <c r="B190" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" s="0" outlineLevel="0">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
       <c r="A191" t="inlineStr">
         <is>
           <t>73001_2</t>
         </is>
       </c>
-      <c r="B191" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" s="0" outlineLevel="0">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
       <c r="A192" t="inlineStr">
         <is>
           <t>73001_3</t>
         </is>
       </c>
-      <c r="B192" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" s="0" outlineLevel="0">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
       <c r="A193" t="inlineStr">
         <is>
           <t>73001_4</t>
         </is>
       </c>
-      <c r="B193" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" s="0" outlineLevel="0">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
       <c r="A194" t="inlineStr">
         <is>
           <t>73006_1</t>
         </is>
       </c>
-      <c r="B194" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" s="0" outlineLevel="0">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
       <c r="A195" t="inlineStr">
         <is>
           <t>73006_10</t>
         </is>
       </c>
-      <c r="B195" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" s="0" outlineLevel="0">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
       <c r="A196" t="inlineStr">
         <is>
           <t>73006_11</t>
         </is>
       </c>
-      <c r="B196" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" s="0" outlineLevel="0">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
       <c r="A197" t="inlineStr">
         <is>
           <t>73006_12</t>
         </is>
       </c>
-      <c r="B197" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" s="0" outlineLevel="0">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
       <c r="A198" t="inlineStr">
         <is>
           <t>73006_13</t>
         </is>
       </c>
-      <c r="B198" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" s="0" outlineLevel="0">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
       <c r="A199" t="inlineStr">
         <is>
           <t>73006_2</t>
         </is>
       </c>
-      <c r="B199" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" s="0" outlineLevel="0">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
       <c r="A200" t="inlineStr">
         <is>
           <t>73006_3</t>
         </is>
       </c>
-      <c r="B200" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" s="0" outlineLevel="0">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
       <c r="A201" t="inlineStr">
         <is>
           <t>73006_4</t>
         </is>
       </c>
-      <c r="B201" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" s="0" outlineLevel="0">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
       <c r="A202" t="inlineStr">
         <is>
           <t>73006_5</t>
         </is>
       </c>
-      <c r="B202" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" s="0" outlineLevel="0">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
       <c r="A203" t="inlineStr">
         <is>
           <t>73006_6</t>
         </is>
       </c>
-      <c r="B203" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" s="0" outlineLevel="0">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>73006_7</t>
         </is>
       </c>
-      <c r="B204" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" s="0" outlineLevel="0">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
       <c r="A205" t="inlineStr">
         <is>
           <t>73006_8</t>
         </is>
       </c>
-      <c r="B205" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" s="0" outlineLevel="0">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
       <c r="A206" t="inlineStr">
         <is>
           <t>73006_9</t>
         </is>
       </c>
-      <c r="B206" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" s="0" outlineLevel="0">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
       <c r="A207" t="inlineStr">
         <is>
           <t>73009_1</t>
         </is>
       </c>
-      <c r="B207" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" s="0" outlineLevel="0">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>73009_2</t>
         </is>
       </c>
-      <c r="B208" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" s="0" outlineLevel="0">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
       <c r="A209" t="inlineStr">
         <is>
           <t>73009_3</t>
         </is>
       </c>
-      <c r="B209" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" s="0" outlineLevel="0">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
       <c r="A210" t="inlineStr">
         <is>
           <t>73009_4</t>
         </is>
       </c>
-      <c r="B210" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" s="0" outlineLevel="0">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
       <c r="A211" t="inlineStr">
         <is>
           <t>73009_5</t>
         </is>
       </c>
-      <c r="B211" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" s="0" outlineLevel="0">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
       <c r="A212" t="inlineStr">
         <is>
           <t>73009_6</t>
         </is>
       </c>
-      <c r="B212" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" s="0" outlineLevel="0">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
       <c r="A213" t="inlineStr">
         <is>
           <t>73009_7</t>
         </is>
       </c>
-      <c r="B213" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" s="0" outlineLevel="0">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
       <c r="A214" t="inlineStr">
         <is>
           <t>73009_8</t>
         </is>
       </c>
-      <c r="B214" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" s="0" outlineLevel="0">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
       <c r="A215" t="inlineStr">
         <is>
           <t>73022_1</t>
         </is>
       </c>
-      <c r="B215" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" s="0" outlineLevel="0">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
           <t>73022_2</t>
         </is>
       </c>
-      <c r="B216" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" s="0" outlineLevel="0">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
       <c r="A217" t="inlineStr">
         <is>
           <t>73022_3</t>
         </is>
       </c>
-      <c r="B217" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" s="0" outlineLevel="0">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
       <c r="A218" t="inlineStr">
         <is>
           <t>73022_4</t>
         </is>
       </c>
-      <c r="B218" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" s="0" outlineLevel="0">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
       <c r="A219" t="inlineStr">
         <is>
           <t>73022_5</t>
         </is>
       </c>
-      <c r="B219" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" s="0" outlineLevel="0">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
       <c r="A220" t="inlineStr">
         <is>
           <t>73022_6</t>
         </is>
       </c>
-      <c r="B220" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" s="0" outlineLevel="0">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
       <c r="A221" t="inlineStr">
         <is>
           <t>73022_7</t>
         </is>
       </c>
-      <c r="B221" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" s="0" outlineLevel="0">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
       <c r="A222" t="inlineStr">
         <is>
           <t>73028_1</t>
         </is>
       </c>
-      <c r="B222" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" s="0" outlineLevel="0">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
       <c r="A223" t="inlineStr">
         <is>
           <t>73032_1</t>
         </is>
       </c>
-      <c r="B223" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" s="0" outlineLevel="0">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
       <c r="A224" t="inlineStr">
         <is>
           <t>73032_2</t>
         </is>
       </c>
-      <c r="B224" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" s="0" outlineLevel="0">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
       <c r="A225" t="inlineStr">
         <is>
           <t>73032_3</t>
         </is>
       </c>
-      <c r="B225" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" s="0" outlineLevel="0">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
       <c r="A226" t="inlineStr">
         <is>
           <t>73032_4</t>
         </is>
       </c>
-      <c r="B226" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" s="0" outlineLevel="0">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
       <c r="A227" t="inlineStr">
         <is>
           <t>73032_5</t>
         </is>
       </c>
-      <c r="B227" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" s="0" outlineLevel="0">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
       <c r="A228" t="inlineStr">
         <is>
           <t>73032_6</t>
         </is>
       </c>
-      <c r="B228" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" s="0" outlineLevel="0">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
       <c r="A229" t="inlineStr">
         <is>
           <t>73032_7</t>
         </is>
       </c>
-      <c r="B229" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" s="0" outlineLevel="0">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
       <c r="A230" t="inlineStr">
         <is>
           <t>73040_1</t>
         </is>
       </c>
-      <c r="B230" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" s="0" outlineLevel="0">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
       <c r="A231" t="inlineStr">
         <is>
           <t>73040_2</t>
         </is>
       </c>
-      <c r="B231" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" s="0" outlineLevel="0">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
       <c r="A232" t="inlineStr">
         <is>
           <t>73040_3</t>
         </is>
       </c>
-      <c r="B232" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" s="0" outlineLevel="0">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
       <c r="A233" t="inlineStr">
         <is>
           <t>73040_4</t>
         </is>
       </c>
-      <c r="B233" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" s="0" outlineLevel="0">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
       <c r="A234" t="inlineStr">
         <is>
           <t>73040_5</t>
         </is>
       </c>
-      <c r="B234" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" s="0" outlineLevel="0">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
       <c r="A235" t="inlineStr">
         <is>
           <t>73042_1</t>
         </is>
       </c>
-      <c r="B235" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" s="0" outlineLevel="0">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
       <c r="A236" t="inlineStr">
         <is>
           <t>73042_2</t>
         </is>
       </c>
-      <c r="B236" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" s="0" outlineLevel="0">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
       <c r="A237" t="inlineStr">
         <is>
           <t>73042_3</t>
         </is>
       </c>
-      <c r="B237" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" s="0" outlineLevel="0">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
       <c r="A238" t="inlineStr">
         <is>
           <t>73042_4</t>
         </is>
       </c>
-      <c r="B238" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" s="0" outlineLevel="0">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
           <t>73042_5</t>
         </is>
       </c>
-      <c r="B239" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" s="0" outlineLevel="0">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
           <t>73042_6</t>
         </is>
       </c>
-      <c r="B240" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" s="0" outlineLevel="0">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
       <c r="A241" t="inlineStr">
         <is>
           <t>73042_7</t>
         </is>
       </c>
-      <c r="B241" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" s="0" outlineLevel="0">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
       <c r="A242" t="inlineStr">
         <is>
           <t>73066_1</t>
         </is>
       </c>
-      <c r="B242" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" s="0" outlineLevel="0">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
       <c r="A243" t="inlineStr">
         <is>
           <t>73066_10</t>
         </is>
       </c>
-      <c r="B243" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" s="0" outlineLevel="0">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
       <c r="A244" t="inlineStr">
         <is>
           <t>73066_11</t>
         </is>
       </c>
-      <c r="B244" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" s="0" outlineLevel="0">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
       <c r="A245" t="inlineStr">
         <is>
           <t>73066_12</t>
         </is>
       </c>
-      <c r="B245" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" s="0" outlineLevel="0">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
       <c r="A246" t="inlineStr">
         <is>
           <t>73066_2</t>
         </is>
       </c>
-      <c r="B246" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" s="0" outlineLevel="0">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
       <c r="A247" t="inlineStr">
         <is>
           <t>73066_3</t>
         </is>
       </c>
-      <c r="B247" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" s="0" outlineLevel="0">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
       <c r="A248" t="inlineStr">
         <is>
           <t>73066_4</t>
         </is>
       </c>
-      <c r="B248" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" s="0" outlineLevel="0">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
       <c r="A249" t="inlineStr">
         <is>
           <t>73066_5</t>
         </is>
       </c>
-      <c r="B249" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" s="0" outlineLevel="0">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
       <c r="A250" t="inlineStr">
         <is>
           <t>73066_6</t>
         </is>
       </c>
-      <c r="B250" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" s="0" outlineLevel="0">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
       <c r="A251" t="inlineStr">
         <is>
           <t>73066_7</t>
         </is>
       </c>
-      <c r="B251" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" s="0" outlineLevel="0">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
       <c r="A252" t="inlineStr">
         <is>
           <t>73066_8</t>
         </is>
       </c>
-      <c r="B252" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" s="0" outlineLevel="0">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
       <c r="A253" t="inlineStr">
         <is>
           <t>73066_9</t>
         </is>
       </c>
-      <c r="B253" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" s="0" outlineLevel="0">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
       <c r="A254" t="inlineStr">
         <is>
           <t>73083_1</t>
         </is>
       </c>
-      <c r="B254" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" s="0" outlineLevel="0">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
       <c r="A255" t="inlineStr">
         <is>
           <t>73083_10</t>
         </is>
       </c>
-      <c r="B255" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" s="0" outlineLevel="0">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
       <c r="A256" t="inlineStr">
         <is>
           <t>73083_11</t>
         </is>
       </c>
-      <c r="B256" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" s="0" outlineLevel="0">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
       <c r="A257" t="inlineStr">
         <is>
           <t>73083_12</t>
         </is>
       </c>
-      <c r="B257" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" s="0" outlineLevel="0">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
       <c r="A258" t="inlineStr">
         <is>
           <t>73083_13</t>
         </is>
       </c>
-      <c r="B258" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" s="0" outlineLevel="0">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
       <c r="A259" t="inlineStr">
         <is>
           <t>73083_14</t>
         </is>
       </c>
-      <c r="B259" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" s="0" outlineLevel="0">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
       <c r="A260" t="inlineStr">
         <is>
           <t>73083_15</t>
         </is>
       </c>
-      <c r="B260" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" s="0" outlineLevel="0">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
       <c r="A261" t="inlineStr">
         <is>
           <t>73083_2</t>
         </is>
       </c>
-      <c r="B261" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" s="0" outlineLevel="0">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
       <c r="A262" t="inlineStr">
         <is>
           <t>73083_3</t>
         </is>
       </c>
-      <c r="B262" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" s="0" outlineLevel="0">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
       <c r="A263" t="inlineStr">
         <is>
           <t>73083_4</t>
         </is>
       </c>
-      <c r="B263" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" s="0" outlineLevel="0">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
       <c r="A264" t="inlineStr">
         <is>
           <t>73083_5</t>
         </is>
       </c>
-      <c r="B264" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" s="0" outlineLevel="0">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
       <c r="A265" t="inlineStr">
         <is>
           <t>73083_6</t>
         </is>
       </c>
-      <c r="B265" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" s="0" outlineLevel="0">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
       <c r="A266" t="inlineStr">
         <is>
           <t>73083_7</t>
         </is>
       </c>
-      <c r="B266" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" s="0" outlineLevel="0">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
       <c r="A267" t="inlineStr">
         <is>
           <t>73083_8</t>
         </is>
       </c>
-      <c r="B267" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" s="0" outlineLevel="0">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
       <c r="A268" t="inlineStr">
         <is>
           <t>73083_9</t>
         </is>
       </c>
-      <c r="B268" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" s="0" outlineLevel="0">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
       <c r="A269" t="inlineStr">
         <is>
           <t>73098_1</t>
         </is>
       </c>
-      <c r="B269" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" s="0" outlineLevel="0">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
       <c r="A270" t="inlineStr">
         <is>
           <t>73098_2</t>
         </is>
       </c>
-      <c r="B270" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" s="0" outlineLevel="0">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
       <c r="A271" t="inlineStr">
         <is>
           <t>73098_3</t>
         </is>
       </c>
-      <c r="B271" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" s="0" outlineLevel="0">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
       <c r="A272" t="inlineStr">
         <is>
           <t>73107_1</t>
         </is>
       </c>
-      <c r="B272" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" s="0" outlineLevel="0">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
       <c r="A273" t="inlineStr">
         <is>
           <t>73107_10</t>
         </is>
       </c>
-      <c r="B273" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" s="0" outlineLevel="0">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
       <c r="A274" t="inlineStr">
         <is>
           <t>73107_2</t>
         </is>
       </c>
-      <c r="B274" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" s="0" outlineLevel="0">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
       <c r="A275" t="inlineStr">
         <is>
           <t>73107_3</t>
         </is>
       </c>
-      <c r="B275" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" s="0" outlineLevel="0">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
       <c r="A276" t="inlineStr">
         <is>
           <t>73107_4</t>
         </is>
       </c>
-      <c r="B276" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" s="0" outlineLevel="0">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
       <c r="A277" t="inlineStr">
         <is>
           <t>73107_5</t>
         </is>
       </c>
-      <c r="B277" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" s="0" outlineLevel="0">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
       <c r="A278" t="inlineStr">
         <is>
           <t>73107_6</t>
         </is>
       </c>
-      <c r="B278" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" s="0" outlineLevel="0">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
       <c r="A279" t="inlineStr">
         <is>
           <t>73107_7</t>
         </is>
       </c>
-      <c r="B279" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" s="0" outlineLevel="0">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
       <c r="A280" t="inlineStr">
         <is>
           <t>73107_8</t>
         </is>
       </c>
-      <c r="B280" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" s="0" outlineLevel="0">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
       <c r="A281" t="inlineStr">
         <is>
           <t>73107_9</t>
         </is>
       </c>
-      <c r="B281" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" s="0" outlineLevel="0">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
       <c r="A282" t="inlineStr">
         <is>
           <t>73109_1</t>
         </is>
       </c>
-      <c r="B282" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" s="0" outlineLevel="0">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
       <c r="A283" t="inlineStr">
         <is>
           <t>73109_2</t>
         </is>
       </c>
-      <c r="B283" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" s="0" outlineLevel="0">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
       <c r="A284" t="inlineStr">
         <is>
           <t>73109_3</t>
         </is>
       </c>
-      <c r="B284" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" s="0" outlineLevel="0">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
       <c r="A285" t="inlineStr">
         <is>
           <t>73109_4</t>
         </is>
       </c>
-      <c r="B285" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" s="0" outlineLevel="0">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
       <c r="A286" t="inlineStr">
         <is>
           <t>RWM_MLO_BG</t>
         </is>
       </c>
-      <c r="B286" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" s="0" outlineLevel="0">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
       <c r="A287" t="inlineStr">
         <is>
           <t>RWM_MLW_BG</t>
         </is>
       </c>
-      <c r="B287" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" s="0" outlineLevel="0">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
       <c r="A288" t="inlineStr">
         <is>
           <t>RWM_NL_BG</t>
         </is>
       </c>
-      <c r="B288" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" s="0" outlineLevel="0">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
       <c r="A289" t="inlineStr">
         <is>
           <t>RWM_NL_RE</t>
         </is>
       </c>
-      <c r="B289" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" s="0" outlineLevel="0">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
       <c r="A290" t="inlineStr">
         <is>
           <t>RWM_NOL_BG</t>
         </is>
       </c>
-      <c r="B290" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" s="0" outlineLevel="0">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
       <c r="A291" t="inlineStr">
         <is>
           <t>RWM_NWL_BG</t>
         </is>
       </c>
-      <c r="B291" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" s="0" outlineLevel="0">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
       <c r="A292" t="inlineStr">
         <is>
           <t>RWM_OL_BG</t>
         </is>
       </c>
-      <c r="B292" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" s="0" outlineLevel="0">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
       <c r="A293" t="inlineStr">
         <is>
           <t>RWM_V_BG</t>
         </is>
       </c>
-      <c r="B293" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" s="0" outlineLevel="0">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
       <c r="A294" t="inlineStr">
         <is>
           <t>RWM_WL_BG</t>
         </is>
       </c>
-      <c r="B294" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" s="0" outlineLevel="0">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
       <c r="A295" t="inlineStr">
         <is>
           <t>RWM_ZOL_BG</t>
         </is>
       </c>
-      <c r="B295" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" s="0" outlineLevel="0">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
       <c r="A296" t="inlineStr">
         <is>
           <t>RWM_ZWL_BG</t>
         </is>
       </c>
-      <c r="B296" s="23">
-        <v>2000</v>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>